--- a/laborator8_students.xlsx
+++ b/laborator8_students.xlsx
@@ -14,16 +14,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
+    <t>Antonia</t>
+  </si>
+  <si>
+    <t>Schiopu</t>
+  </si>
+  <si>
     <t>Alexandru</t>
   </si>
   <si>
     <t>Salaghe</t>
-  </si>
-  <si>
-    <t>Antonia</t>
-  </si>
-  <si>
-    <t>Schiopu</t>
   </si>
   <si>
     <t>Flavius</t>
@@ -85,7 +85,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n" s="0">
-        <v>10555.0</v>
+        <v>10234.0</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -99,7 +99,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
-        <v>10234.0</v>
+        <v>10555.0</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>2</v>
